--- a/data/processed/y_test.xlsx
+++ b/data/processed/y_test.xlsx
@@ -430,7 +430,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -460,32 +460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -505,7 +505,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -515,7 +515,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -525,7 +525,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -540,7 +540,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -550,12 +550,12 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -575,22 +575,22 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -600,7 +600,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -650,7 +650,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -660,7 +660,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -675,12 +675,12 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -690,12 +690,12 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -705,7 +705,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -715,12 +715,12 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -740,7 +740,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -760,7 +760,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -770,12 +770,12 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -785,12 +785,12 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -800,7 +800,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -810,7 +810,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -820,7 +820,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -860,7 +860,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -890,7 +890,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -900,7 +900,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -925,12 +925,12 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -940,12 +940,12 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -955,7 +955,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -965,7 +965,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -980,7 +980,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -1000,7 +1000,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -1020,7 +1020,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -1050,22 +1050,22 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -1075,12 +1075,12 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -1095,22 +1095,22 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -1125,17 +1125,17 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -1145,7 +1145,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -1165,12 +1165,12 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -1180,12 +1180,12 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
